--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2311-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2311-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62BE9319-8963-4FF4-8932-F5BABE9F9FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F1CE45-8A41-4C64-A362-29EAF3ADE6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{11C50D82-1A49-40A4-9986-246DD2116B96}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E26DF511-5A4C-4B1E-849B-32E3D30B9299}"/>
   </bookViews>
   <sheets>
     <sheet name="2311-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1484,25 +1484,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCAD6A20-06DD-4BE5-8B1A-85C357DAA0B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6168221A-6571-4BDA-82A5-69EDB9802F0A}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1535,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1572,7 +1571,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1624,7 +1623,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1692,7 +1691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2022</v>
       </c>
@@ -1764,7 +1763,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2021</v>
       </c>
@@ -1836,7 +1835,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2020</v>
       </c>
@@ -1908,7 +1907,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2019</v>
       </c>
@@ -1980,7 +1979,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2018</v>
       </c>
@@ -2052,7 +2051,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2017</v>
       </c>
@@ -2124,7 +2123,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2016</v>
       </c>
@@ -2196,7 +2195,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2015</v>
       </c>
@@ -2268,7 +2267,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2014</v>
       </c>
@@ -2340,7 +2339,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2013</v>
       </c>
@@ -2412,7 +2411,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2012</v>
       </c>
@@ -2484,7 +2483,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2011</v>
       </c>
@@ -2556,7 +2555,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2010</v>
       </c>
@@ -2628,7 +2627,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2009</v>
       </c>
@@ -2700,7 +2699,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2008</v>
       </c>
@@ -2772,7 +2771,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2007</v>
       </c>
@@ -2844,7 +2843,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2006</v>
       </c>
@@ -2916,7 +2915,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2005</v>
       </c>
@@ -2988,7 +2987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2004</v>
       </c>
@@ -3060,7 +3059,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2003</v>
       </c>
@@ -3132,7 +3131,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2002</v>
       </c>
@@ -3204,7 +3203,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2001</v>
       </c>
@@ -3276,7 +3275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2000</v>
       </c>
@@ -3348,7 +3347,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>1999</v>
       </c>
@@ -3420,7 +3419,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>1998</v>
       </c>
@@ -3492,7 +3491,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>1997</v>
       </c>
@@ -3564,7 +3563,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>1996</v>
       </c>
@@ -3636,7 +3635,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>1995</v>
       </c>
@@ -3708,7 +3707,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>1994</v>
       </c>
@@ -3780,7 +3779,7 @@
         <v>7.44</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>1993</v>
       </c>
@@ -3852,7 +3851,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
         <v>1992</v>
       </c>
@@ -3924,7 +3923,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>1991</v>
       </c>
@@ -3996,7 +3995,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>1990</v>
       </c>
@@ -4068,7 +4067,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>1989</v>
       </c>
@@ -4140,7 +4139,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
         <v>1988</v>
       </c>
@@ -4212,7 +4211,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>1987</v>
       </c>
@@ -4284,7 +4283,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
         <v>1986</v>
       </c>
@@ -4356,7 +4355,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35" t="s">
         <v>54</v>
       </c>
